--- a/public/assets/BOs/Fuxi.xlsx
+++ b/public/assets/BOs/Fuxi.xlsx
@@ -1,31 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\doc\coding\DoD\DeitiesOfDeath\public\assets\BOs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Chris\OneDrive\Github\Deities of Death\public\assets\BOs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F6EC74B-B456-4054-AB67-F9B776B77C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{039A8AD3-01D9-497B-873D-0BF1E612A5DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="3" r:id="rId1"/>
-    <sheet name="Feuil5" sheetId="7" r:id="rId2"/>
-    <sheet name="Feuil2" sheetId="4" r:id="rId3"/>
-    <sheet name="Feuil3" sheetId="5" r:id="rId4"/>
-    <sheet name="Feuil4" sheetId="6" r:id="rId5"/>
-    <sheet name="Tabelle1" sheetId="1" r:id="rId6"/>
+    <sheet name="Feuil1" sheetId="8" r:id="rId1"/>
+    <sheet name="Feuil6" sheetId="9" r:id="rId2"/>
+    <sheet name="Feuil5" sheetId="7" r:id="rId3"/>
+    <sheet name="Feuil2" sheetId="4" r:id="rId4"/>
+    <sheet name="Feuil3" sheetId="5" r:id="rId5"/>
+    <sheet name="Feuil4" sheetId="6" r:id="rId6"/>
+    <sheet name="Tabelle1" sheetId="1" r:id="rId7"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="129">
   <si>
     <t>Archaic</t>
   </si>
@@ -84,249 +85,7 @@
     <t>Food / Wood / Gold / Favor</t>
   </si>
   <si>
-    <t>1 Peasant makes a Silo then goes on Wood</t>
-  </si>
-  <si>
-    <t>7 Peasants on Food</t>
-  </si>
-  <si>
-    <t>Once you have 250 gold move Kuafu to Wood</t>
-  </si>
-  <si>
-    <t>1 Kuafu on Gold</t>
-  </si>
-  <si>
-    <t>Advance (2.30)</t>
-  </si>
-  <si>
-    <t>Classical (3.30)</t>
-  </si>
-  <si>
     <t>OUTDATED - Fast 2 TC + 3 Kua Fu + Nezha - By Looki</t>
-  </si>
-  <si>
-    <r>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / 0 / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / 0</t>
-    </r>
-  </si>
-  <si>
-    <t>1 Peasant makes a Silo then goes on Food
-1 Peasant makes a house then goes on Food
-Kuafu makes a Silo then goes on Gold</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">2 / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / 1 / 0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">9 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>/ 1 /</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>1 / 0</t>
-    </r>
-  </si>
-  <si>
-    <t>Kuafu makes temple once you have 150 Wood</t>
-  </si>
-  <si>
-    <r>
-      <t>9</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">/ </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> /</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / 0</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> /</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> 4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / 2 / 0</t>
-    </r>
-  </si>
-  <si>
-    <t>Move 2 Peasants from Food to Wood
-Move 1 Peasant from Food to Gold</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">6 / 4 / </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> / 0</t>
-    </r>
-  </si>
-  <si>
-    <t>3:30 double Kuafu - Mirez</t>
   </si>
   <si>
     <t>All new villagers go to food</t>
@@ -630,18 +389,560 @@
   <si>
     <t>Pickaxe/Handaxe 2 Kuafus - By Motaba</t>
   </si>
+  <si>
+    <t>1 Peasant builds a Silo then goes on Food
+1 Peasant makes a Silo then goes on Gold
+Kuafu makes a House, a Silo then goes on Wood</t>
+  </si>
+  <si>
+    <t>Kuafu on Wood</t>
+  </si>
+  <si>
+    <t>Kuafu builds Temple when you have 150 Gold</t>
+  </si>
+  <si>
+    <t>Advance (3:18)</t>
+  </si>
+  <si>
+    <t>Redistrubite peasants to wood and gold based on gameplan</t>
+  </si>
+  <si>
+    <t>Classical (4:18)</t>
+  </si>
+  <si>
+    <t>Fuxi - 4:18 tripple Kuafu V2 - Mirez</t>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>Place Peach Blossom Spring for extra favoured land</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">7 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/ 1 /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1 / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>6 Peasants on Food</t>
+  </si>
+  <si>
+    <t>Once you have 150 wood move Kuafu to Gold</t>
+  </si>
+  <si>
+    <r>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>Kuafu on Gold</t>
+  </si>
+  <si>
+    <r>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2 / 0</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / 2 / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>Fuxi - 3:33 Double Kuafu V2 - Mirez</t>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / 0 / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>1 Peasant builds a Silo then goes on Food
+1 Peasant builds a House then goes on Food
+Kuafu makes a Silo then goes on Gold</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">8 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>/ 0 / 1 / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>Once you have 250 Gold move Kuafu to Wood (build Silo)</t>
+  </si>
+  <si>
+    <r>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">/ </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>Kuafu builds Temple when you have 150 Wood</t>
+  </si>
+  <si>
+    <t>Advance (2:33)</t>
+  </si>
+  <si>
+    <r>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> /</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> / 0</t>
+    </r>
+  </si>
+  <si>
+    <t>Classical (3:33)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="16">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Inherit"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Inherit"/>
     </font>
     <font>
       <b/>
@@ -658,62 +959,10 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="13"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="7">
@@ -722,18 +971,6 @@
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -751,6 +988,18 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
@@ -817,52 +1066,64 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1203,129 +1464,124 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F763F477-866C-4C8C-9F90-45B659FC8F6E}">
-  <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4449A1E9-4010-4732-A1A2-0B06B5295967}">
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5"/>
+  <cols>
+    <col min="1" max="16384" width="11" style="5"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="36" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="B1" s="9"/>
-      <c r="C1" s="9"/>
-      <c r="D1" s="10"/>
-    </row>
-    <row r="2" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="11" t="s">
+    <row r="1" spans="1:4" ht="18.5" thickBot="1">
+      <c r="A1" s="18" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="20"/>
+    </row>
+    <row r="2" spans="1:4" ht="16" thickBot="1">
+      <c r="A2" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="13"/>
-    </row>
-    <row r="3" spans="1:4" ht="44.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="23"/>
+    </row>
+    <row r="3" spans="1:4" ht="43" thickBot="1">
+      <c r="A3" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:4" ht="215.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-    </row>
-    <row r="5" spans="1:4" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-    </row>
-    <row r="6" spans="1:4" ht="72.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-    </row>
-    <row r="8" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="11" t="s">
-        <v>23</v>
-      </c>
-      <c r="B8" s="12"/>
-      <c r="C8" s="12"/>
-      <c r="D8" s="13"/>
-    </row>
-    <row r="9" spans="1:4" ht="44.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+    </row>
+    <row r="4" spans="1:4" ht="211" thickBot="1">
+      <c r="A4" s="17" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="16"/>
+    </row>
+    <row r="5" spans="1:4" ht="71" thickBot="1">
+      <c r="A5" s="17" t="s">
+        <v>112</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" s="16"/>
+    </row>
+    <row r="6" spans="1:4" ht="29" thickBot="1">
+      <c r="A6" s="15" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+    </row>
+    <row r="7" spans="1:4" ht="71" thickBot="1">
+      <c r="A7" s="15" t="s">
+        <v>117</v>
+      </c>
+      <c r="B7" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="C7" s="15" t="s">
+        <v>105</v>
+      </c>
+      <c r="D7" s="16"/>
+    </row>
+    <row r="8" spans="1:4" ht="16" thickBot="1">
+      <c r="A8" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="23"/>
+    </row>
+    <row r="9" spans="1:4" ht="43" thickBot="1">
+      <c r="A9" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-    </row>
-    <row r="10" spans="1:4" ht="115.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-    </row>
-    <row r="11" spans="1:4" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="12"/>
-      <c r="D11" s="13"/>
-    </row>
-    <row r="12" spans="1:4" ht="44.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+    </row>
+    <row r="10" spans="1:4" ht="71" thickBot="1">
+      <c r="A10" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+    </row>
+    <row r="11" spans="1:4" ht="16" thickBot="1">
+      <c r="A11" s="21" t="s">
+        <v>108</v>
+      </c>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="23"/>
+    </row>
+    <row r="12" spans="1:4" ht="43" thickBot="1">
+      <c r="A12" s="15" t="s">
         <v>18</v>
       </c>
-      <c r="B12" s="2"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="2"/>
-    </row>
-    <row r="13" spans="1:4" ht="30" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C13" s="2"/>
-      <c r="D13" s="2"/>
+      <c r="B12" s="16"/>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1339,122 +1595,289 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CFB13DDB-3E40-4CF6-B4E9-2C767FDD0920}">
+  <dimension ref="A1:D22"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
+  <sheetData>
+    <row r="1" spans="1:4" ht="18.5" thickBot="1">
+      <c r="A1" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="20"/>
+    </row>
+    <row r="2" spans="1:4" ht="16" thickBot="1">
+      <c r="A2" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="23"/>
+    </row>
+    <row r="3" spans="1:4" ht="57" thickBot="1">
+      <c r="A3" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="16"/>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+    </row>
+    <row r="4" spans="1:4" ht="197" thickBot="1">
+      <c r="A4" s="17" t="s">
+        <v>120</v>
+      </c>
+      <c r="B4" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" s="16"/>
+    </row>
+    <row r="5" spans="1:4" ht="85" thickBot="1">
+      <c r="A5" s="17" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>123</v>
+      </c>
+      <c r="D5" s="16"/>
+    </row>
+    <row r="6" spans="1:4" ht="71" thickBot="1">
+      <c r="A6" s="15" t="s">
+        <v>124</v>
+      </c>
+      <c r="B6" s="15" t="s">
+        <v>116</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="D6" s="16"/>
+    </row>
+    <row r="7" spans="1:4" ht="16" thickBot="1">
+      <c r="A7" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="23"/>
+    </row>
+    <row r="8" spans="1:4" ht="57" thickBot="1">
+      <c r="A8" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+    </row>
+    <row r="9" spans="1:4" ht="85" thickBot="1">
+      <c r="A9" s="17" t="s">
+        <v>127</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+    </row>
+    <row r="10" spans="1:4" ht="16" thickBot="1">
+      <c r="A10" s="21" t="s">
+        <v>128</v>
+      </c>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="23"/>
+    </row>
+    <row r="11" spans="1:4" ht="57" thickBot="1">
+      <c r="A11" s="15" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="16"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="6"/>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="6"/>
+      <c r="B13" s="6"/>
+      <c r="C13" s="6"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="11"/>
+      <c r="B15" s="10"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="10"/>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="7"/>
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="7"/>
+      <c r="B17" s="1"/>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="7"/>
+      <c r="B18" s="8"/>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="9"/>
+      <c r="B19" s="1"/>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="8"/>
+      <c r="B20" s="1"/>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="9"/>
+      <c r="B21" s="1"/>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="8"/>
+      <c r="B22" s="1"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A15:D15"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A8E654D3-AF4A-4D6F-AE6A-3E7B3599F3AF}">
   <dimension ref="A1:D17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4">
       <c r="A3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4">
       <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
+        <v>87</v>
+      </c>
+      <c r="B6" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="C10" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
         <v>96</v>
       </c>
-      <c r="B4" t="s">
+      <c r="C12" t="s">
         <v>97</v>
       </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="13" spans="1:4">
+      <c r="C13" t="s">
         <v>98</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D13" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="15" spans="1:4">
+      <c r="A15" t="s">
         <v>100</v>
       </c>
-      <c r="B5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>103</v>
-      </c>
-      <c r="B6" t="s">
-        <v>104</v>
-      </c>
-      <c r="C6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C10" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>106</v>
-      </c>
-      <c r="B11" t="s">
-        <v>109</v>
-      </c>
-      <c r="C11" t="s">
-        <v>110</v>
-      </c>
-      <c r="D11" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C12" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="C13" t="s">
-        <v>114</v>
-      </c>
-      <c r="D13" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:4">
       <c r="A16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3">
       <c r="A17" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>117</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
@@ -1462,144 +1885,144 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4845777-F807-476E-B94C-F651C8575ECC}">
   <dimension ref="A1:D15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
-        <v>55</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-    </row>
-    <row r="2" spans="1:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+    <row r="1" spans="1:4" ht="19.5">
+      <c r="A1" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+    </row>
+    <row r="2" spans="1:4" ht="21">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-    </row>
-    <row r="3" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+    </row>
+    <row r="3" spans="1:4" ht="17">
+      <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="17">
+      <c r="A9" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" ht="17">
+      <c r="A11" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="3"/>
+      <c r="B12" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="C13" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>44</v>
-      </c>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-    </row>
-    <row r="9" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="6"/>
-      <c r="B12" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B13" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6"/>
-      <c r="B14" s="6"/>
-      <c r="C14" s="6"/>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="6"/>
-      <c r="C15" s="4"/>
-      <c r="D15" s="4"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1612,166 +2035,166 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BBCD348-4135-4A44-88D7-C13E373323DB}">
   <dimension ref="A1:D18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
-        <v>95</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-    </row>
-    <row r="2" spans="1:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+    <row r="1" spans="1:4" ht="19.5">
+      <c r="A1" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+    </row>
+    <row r="2" spans="1:4" ht="21">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-    </row>
-    <row r="3" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+    </row>
+    <row r="3" spans="1:4" ht="17">
+      <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="6" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3"/>
+      <c r="B5" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="4"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+    </row>
+    <row r="9" spans="1:4" ht="17">
+      <c r="A9" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B9" s="10"/>
+      <c r="C9" s="10"/>
+      <c r="D9" s="10"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C10" s="3"/>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" ht="17">
+      <c r="A11" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="1"/>
+      <c r="B13" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="3"/>
+      <c r="D13" s="1"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D14" s="1"/>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="1"/>
+      <c r="B15" s="1"/>
+      <c r="C15" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="D15" s="1"/>
+    </row>
+    <row r="16" spans="1:4" ht="17">
+      <c r="A16" s="14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B16" s="10"/>
+      <c r="C16" s="10"/>
+      <c r="D16" s="10"/>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="D17" s="1"/>
+    </row>
+    <row r="18" spans="1:4" ht="17">
+      <c r="A18" s="14" t="s">
         <v>57</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="6"/>
-      <c r="B5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-    </row>
-    <row r="9" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A9" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B9" s="15"/>
-      <c r="C9" s="15"/>
-      <c r="D9" s="15"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" s="6"/>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="6" t="s">
-        <v>64</v>
-      </c>
-      <c r="B12" s="4"/>
-      <c r="C12" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="4"/>
-      <c r="B13" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="6"/>
-      <c r="D13" s="4"/>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="B14" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D14" s="4"/>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A15" s="4"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D15" s="4"/>
-    </row>
-    <row r="16" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A17" s="4"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="6" t="s">
-        <v>72</v>
-      </c>
-      <c r="D17" s="4"/>
-    </row>
-    <row r="18" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
-        <v>73</v>
-      </c>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
+      <c r="B18" s="10"/>
+      <c r="C18" s="10"/>
+      <c r="D18" s="10"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1786,134 +2209,134 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B0DA1104-723F-4704-99AD-7EFB6062E50F}">
   <dimension ref="A1:D13"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <sheetData>
-    <row r="1" spans="1:4" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="14" t="s">
-        <v>94</v>
-      </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
-    </row>
-    <row r="2" spans="1:4" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="16" t="s">
+    <row r="1" spans="1:4" ht="19.5">
+      <c r="A1" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+    </row>
+    <row r="2" spans="1:4" ht="21">
+      <c r="A2" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="15"/>
-      <c r="C2" s="15"/>
-      <c r="D2" s="15"/>
-    </row>
-    <row r="3" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+    </row>
+    <row r="3" spans="1:4" ht="17">
+      <c r="A3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="4"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="6" t="s">
+      <c r="B3" s="1"/>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="1"/>
+      <c r="B4" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="1"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="D5" s="1"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D6" s="1"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+    </row>
+    <row r="8" spans="1:4" ht="17">
+      <c r="A8" s="14" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="10"/>
+      <c r="C8" s="10"/>
+      <c r="D8" s="10"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="1"/>
+    </row>
+    <row r="11" spans="1:4" ht="17">
+      <c r="A11" s="14" t="s">
         <v>74</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="B11" s="10"/>
+      <c r="C11" s="10"/>
+      <c r="D11" s="10"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="1"/>
+      <c r="B12" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="4"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="6" t="s">
+      <c r="C12" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="D12" s="1"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="3"/>
+      <c r="B13" s="3"/>
+      <c r="C13" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="6" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" s="4"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>81</v>
-      </c>
-      <c r="D6" s="4"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="6" t="s">
-        <v>82</v>
-      </c>
-      <c r="B7" s="6" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-    </row>
-    <row r="8" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="B8" s="15"/>
-      <c r="C8" s="15"/>
-      <c r="D8" s="15"/>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="6" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="6" t="s">
-        <v>88</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>89</v>
-      </c>
-      <c r="D10" s="4"/>
-    </row>
-    <row r="11" spans="1:4" ht="17.25" x14ac:dyDescent="0.3">
-      <c r="A11" s="17" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="15"/>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="4"/>
-      <c r="B12" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12" s="4"/>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="6"/>
-      <c r="B13" s="6"/>
-      <c r="C13" s="6" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" s="4"/>
+      <c r="D13" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1926,27 +2349,27 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C15"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="15.5"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>2</v>
       </c>
@@ -1957,7 +2380,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1965,7 +2388,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -1973,7 +2396,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -1981,7 +2404,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -1989,37 +2412,37 @@
         <v>12</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3">
       <c r="A9" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3">
       <c r="A10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3">
       <c r="B13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3">
       <c r="B14" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3">
       <c r="B15" t="s">
         <v>17</v>
       </c>
